--- a/web/public/forms/gongsa-daegeum.xlsx
+++ b/web/public/forms/gongsa-daegeum.xlsx
@@ -604,7 +604,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="23" t="inlineStr">

--- a/web/public/forms/gongsa-daegeum.xlsx
+++ b/web/public/forms/gongsa-daegeum.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공사대금 청구서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'공사대금 청구서'!$A$1:$X$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -203,9 +201,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -838,16 +833,10 @@
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
-      <c r="O12" s="12">
-        <f>IF(K12="","",INT(ROUND(K12*0.1,6)))</f>
-        <v/>
-      </c>
+      <c r="O12" s="12" t="n"/>
       <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="12">
-        <f>IF(K12="","",K12+O12)</f>
-        <v/>
-      </c>
+      <c r="R12" s="12" t="n"/>
       <c r="S12" s="5" t="n"/>
       <c r="T12" s="5" t="n"/>
       <c r="U12" s="5" t="n"/>
@@ -870,16 +859,10 @@
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
-      <c r="O13" s="12">
-        <f>IF(K13="","",INT(ROUND(K13*0.1,6)))</f>
-        <v/>
-      </c>
+      <c r="O13" s="12" t="n"/>
       <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="12">
-        <f>IF(K13="","",K13+O13)</f>
-        <v/>
-      </c>
+      <c r="R13" s="12" t="n"/>
       <c r="S13" s="5" t="n"/>
       <c r="T13" s="5" t="n"/>
       <c r="U13" s="5" t="n"/>
@@ -902,16 +885,10 @@
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n"/>
       <c r="N14" s="5" t="n"/>
-      <c r="O14" s="12">
-        <f>IF(K14="","",INT(ROUND(K14*0.1,6)))</f>
-        <v/>
-      </c>
+      <c r="O14" s="12" t="n"/>
       <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="12">
-        <f>IF(K14="","",K14+O14)</f>
-        <v/>
-      </c>
+      <c r="R14" s="12" t="n"/>
       <c r="S14" s="5" t="n"/>
       <c r="T14" s="5" t="n"/>
       <c r="U14" s="5" t="n"/>
@@ -934,16 +911,10 @@
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
-      <c r="O15" s="12">
-        <f>IF(K15="","",INT(ROUND(K15*0.1,6)))</f>
-        <v/>
-      </c>
+      <c r="O15" s="12" t="n"/>
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="12">
-        <f>IF(K15="","",K15+O15)</f>
-        <v/>
-      </c>
+      <c r="R15" s="12" t="n"/>
       <c r="S15" s="5" t="n"/>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
@@ -966,16 +937,10 @@
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="n"/>
-      <c r="O16" s="12">
-        <f>IF(K16="","",INT(ROUND(K16*0.1,6)))</f>
-        <v/>
-      </c>
+      <c r="O16" s="12" t="n"/>
       <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="12">
-        <f>IF(K16="","",K16+O16)</f>
-        <v/>
-      </c>
+      <c r="R16" s="12" t="n"/>
       <c r="S16" s="5" t="n"/>
       <c r="T16" s="5" t="n"/>
       <c r="U16" s="5" t="n"/>
@@ -998,16 +963,10 @@
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="5" t="n"/>
-      <c r="O17" s="12">
-        <f>IF(K17="","",INT(ROUND(K17*0.1,6)))</f>
-        <v/>
-      </c>
+      <c r="O17" s="12" t="n"/>
       <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="12">
-        <f>IF(K17="","",K17+O17)</f>
-        <v/>
-      </c>
+      <c r="R17" s="12" t="n"/>
       <c r="S17" s="5" t="n"/>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
@@ -1030,23 +989,14 @@
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
-      <c r="K18" s="14">
-        <f>SUM(K12:K17)</f>
-        <v/>
-      </c>
+      <c r="K18" s="14" t="n"/>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="5" t="n"/>
       <c r="N18" s="5" t="n"/>
-      <c r="O18" s="14">
-        <f>SUM(O12:O17)</f>
-        <v/>
-      </c>
+      <c r="O18" s="14" t="n"/>
       <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="14">
-        <f>SUM(R12:R17)</f>
-        <v/>
-      </c>
+      <c r="R18" s="14" t="n"/>
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
@@ -1156,10 +1106,7 @@
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="12">
-        <f>IF(COUNT(R12:R17)=0,"",SUM(R12:R17))</f>
-        <v/>
-      </c>
+      <c r="G23" s="12" t="n"/>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
@@ -1189,10 +1136,7 @@
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="15">
-        <f>G23</f>
-        <v/>
-      </c>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
@@ -1222,10 +1166,7 @@
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="12">
-        <f>IF(G23="","",IF(N(G21)&gt;0,N(G21),N(G20))-N(G22)-G23)</f>
-        <v/>
-      </c>
+      <c r="G25" s="12" t="n"/>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
@@ -1336,6 +1277,7 @@
       </c>
     </row>
     <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="22" t="inlineStr">
         <is>
@@ -1449,934 +1391,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>공 사 대 금 청 구 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  수    신</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>예시종합건설(주) 대표이사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사 중 배수관 부설</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공사장소</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>가나시 다라동 123-4 일원</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계약일자</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="7" t="n">
-        <v>46101</v>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공사기간</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>2026. 3. 23. ~ 2026. 11. 30.</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>청구 내용</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>공급가액</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>부가가치세</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>합  계</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>기성</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>제3회 기성 — 8월분 (배수관 D600 부설 420m)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="11" t="n">
-        <v>98500000</v>
-      </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="12">
-        <f>IF(K12="","",INT(ROUND(K12*0.1,6)))</f>
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="12">
-        <f>IF(K12="","",K12+O12)</f>
-        <v/>
-      </c>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="9" t="inlineStr">
-        <is>
-          <t>기성 확인서 첨부</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>추가공사</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>집수정 2개소 추가 (9. 2. 현장 지시)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="11" t="n">
-        <v>6400000</v>
-      </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="12">
-        <f>IF(K13="","",INT(ROUND(K13*0.1,6)))</f>
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="12">
-        <f>IF(K13="","",K13+O13)</f>
-        <v/>
-      </c>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="9" t="inlineStr">
-        <is>
-          <t>지시서 사본</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="12">
-        <f>IF(K14="","",INT(ROUND(K14*0.1,6)))</f>
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="12">
-        <f>IF(K14="","",K14+O14)</f>
-        <v/>
-      </c>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="9" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="12">
-        <f>IF(K15="","",INT(ROUND(K15*0.1,6)))</f>
-        <v/>
-      </c>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="12">
-        <f>IF(K15="","",K15+O15)</f>
-        <v/>
-      </c>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="9" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="11" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="12">
-        <f>IF(K16="","",INT(ROUND(K16*0.1,6)))</f>
-        <v/>
-      </c>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="12">
-        <f>IF(K16="","",K16+O16)</f>
-        <v/>
-      </c>
-      <c r="S16" s="5" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="9" t="n"/>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="11" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="12">
-        <f>IF(K17="","",INT(ROUND(K17*0.1,6)))</f>
-        <v/>
-      </c>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="12">
-        <f>IF(K17="","",K17+O17)</f>
-        <v/>
-      </c>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="9" t="n"/>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>합        계</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="14">
-        <f>SUM(K12:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="14">
-        <f>SUM(O12:O17)</f>
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="14">
-        <f>SUM(R12:R17)</f>
-        <v/>
-      </c>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="13" t="inlineStr"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="6" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계약금액</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="11" t="n">
-        <v>412500000</v>
-      </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  변경 계약금액</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="11" t="n">
-        <v>428900000</v>
-      </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  기지급액(누계)</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="11" t="n">
-        <v>214450000</v>
-      </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  금회 청구금액</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="12">
-        <f>IF(COUNT(R12:R17)=0,"",SUM(R12:R17))</f>
-        <v/>
-      </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  금회 청구금액(한글)</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="15">
-        <f>G23</f>
-        <v/>
-      </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  청구 후 남는 금액</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="12">
-        <f>IF(G23="","",IF(N(G21)&gt;0,N(G21),N(G20))-N(G22)-G23)</f>
-        <v/>
-      </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  지급 기한</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="7" t="n">
-        <v>46310</v>
-      </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n"/>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  입금 계좌</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>예시은행 000-000000-00-000 (예금주 가나토건(주))</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="5" t="n"/>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>위 공사의 대금을 위와 같이 청구하오니 지급 기한까지 위 계좌로 지급하여 주시기 바랍니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="10" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="17" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="18" t="inlineStr"/>
-      <c r="K33" s="19" t="inlineStr">
-        <is>
-          <t>청구인(수급인) 대표자</t>
-        </is>
-      </c>
-      <c r="Q33" s="20" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U33" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="6" customHeight="1"/>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="83">
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A32:X32"/>
-    <mergeCell ref="G20:X20"/>
-    <mergeCell ref="A29:X29"/>
-    <mergeCell ref="R13:U13"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="V12:X12"/>
-    <mergeCell ref="G22:X22"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="G21:X21"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="G23:X23"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="R18:U18"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="G24:X24"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="G26:X26"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="G25:X25"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="R16:U16"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="G8:X8"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="V18:X18"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="G27:X27"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="R17:U17"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="R14:U14"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="R11:U11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="Q33:T33"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="R15:U15"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="A36:X36"/>
-    <mergeCell ref="A25:F25"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/gongsa-daegeum.xlsx
+++ b/web/public/forms/gongsa-daegeum.xlsx
@@ -599,7 +599,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
